--- a/artfynd/A 10436-2022 artfynd.xlsx
+++ b/artfynd/A 10436-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 10436-2022 artfynd.xlsx
+++ b/artfynd/A 10436-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99527656</v>
+        <v>100445309</v>
       </c>
       <c r="B2" t="n">
-        <v>8367</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,51 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tingtjärnen, Hofors, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573336.0809952527</v>
+        <v>573430</v>
       </c>
       <c r="R2" t="n">
-        <v>6702270.471847746</v>
+        <v>6702213</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -762,27 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-03-26</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På björklåga</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,71 +765,82 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maj-Lis Koivisto, Nicklas Gustavsson</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>100444260</v>
+        <v>100443117</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573505.0008457641</v>
+        <v>573485</v>
       </c>
       <c r="R3" t="n">
-        <v>6702302.521804534</v>
+        <v>6702372</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -887,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:14</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -897,12 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>100-tal bladrosetter, 3 vinterståndare</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,65 +909,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>100443287</v>
+        <v>100445522</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573481.1899096592</v>
+        <v>573421</v>
       </c>
       <c r="R4" t="n">
-        <v>6702428.388085248</v>
+        <v>6702316</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1019,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>19:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1056,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100445309</v>
+        <v>99527656</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>8444</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1072,35 +1034,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>106554</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hofors, Gstr</t>
+          <t>Tingtjärnen, Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573430.1949939872</v>
+        <v>573336</v>
       </c>
       <c r="R5" t="n">
-        <v>6702212.656419976</v>
+        <v>6702270</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1127,22 +1105,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>19:39</t>
+          <t>2022-03-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2022-05-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>19:39</t>
+          <t>2022-03-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På björklåga</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,33 +1124,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Maj-Lis Koivisto</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Maj-Lis Koivisto, Nicklas Gustavsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100444744</v>
+        <v>100443287</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1204,7 +1173,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1212,7 +1181,11 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1220,10 +1193,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573504.1990141788</v>
+        <v>573481</v>
       </c>
       <c r="R6" t="n">
-        <v>6702268.943255903</v>
+        <v>6702428</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1255,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1265,7 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>19:27</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1292,15 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>105310472</v>
+        <v>100444260</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1326,19 +1294,21 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Gillermossen, Gstr</t>
+          <t>Hofors, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573506.1293200894</v>
+        <v>573505</v>
       </c>
       <c r="R7" t="n">
-        <v>6702295.634844949</v>
+        <v>6702303</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1362,22 +1332,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-05-16</t>
+          <t>2022-05-02</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>19:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>100-tal bladrosetter, 3 vinterståndare</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1388,29 +1363,244 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Ca 100 rosetter</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>Henrik Tykosson</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>100444744</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hofors, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>573504</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6702269</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-05-02</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-05-02</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>19:27</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Philipp Weiss</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>105310472</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gillermossen, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>573506</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6702296</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hofors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Torsåker</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-05-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Ca 100 rosetter</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Helene Andersson</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>Henrik Tykosson</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 10436-2022 artfynd.xlsx
+++ b/artfynd/A 10436-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100445309</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100443117</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100445522</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99527656</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100443287</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1376,6 +1406,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100444260</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1494,6 +1529,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100444744</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1601,8 +1641,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105310472</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>